--- a/marketing_report/outputs/Grado_Pregrado/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>368,960</t>
+          <t>398,401</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>286,461</t>
+          <t>305,011</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>152,095</t>
+          <t>169,894</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8,586</t>
+          <t>10,225</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7,020</t>
+          <t>7,980</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,892</t>
+          <t>6,911</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6,926</t>
+          <t>7,993</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,641</t>
+          <t>1,377</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5,847</t>
+          <t>6,933</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>451</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.33%</t>
+          <t>6.51%</t>
         </is>
       </c>
     </row>
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>228227</v>
+        <v>238011</v>
       </c>
       <c r="C2" t="n">
-        <v>118064</v>
+        <v>128716</v>
       </c>
       <c r="D2" t="n">
-        <v>2753</v>
+        <v>3014</v>
       </c>
       <c r="E2" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="3">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58234</v>
+        <v>67000</v>
       </c>
       <c r="C3" t="n">
-        <v>34031</v>
+        <v>41178</v>
       </c>
       <c r="D3" t="n">
-        <v>3139</v>
+        <v>3897</v>
       </c>
       <c r="E3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>189858</v>
+        <v>201690</v>
       </c>
       <c r="C2" t="n">
-        <v>106547</v>
+        <v>117504</v>
       </c>
       <c r="D2" t="n">
-        <v>630</v>
+        <v>683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="3">
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19790</v>
+        <v>20625</v>
       </c>
       <c r="C3" t="n">
-        <v>8295</v>
+        <v>9186</v>
       </c>
       <c r="D3" t="n">
-        <v>1155</v>
+        <v>1263</v>
       </c>
       <c r="E3" t="n">
-        <v>13.92</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="4">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18336</v>
+        <v>19062</v>
       </c>
       <c r="C4" t="n">
-        <v>7434</v>
+        <v>8197</v>
       </c>
       <c r="D4" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="5">
@@ -809,16 +809,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17356</v>
+        <v>18679</v>
       </c>
       <c r="C5" t="n">
-        <v>10208</v>
+        <v>11626</v>
       </c>
       <c r="D5" t="n">
-        <v>1121</v>
+        <v>1258</v>
       </c>
       <c r="E5" t="n">
-        <v>10.98</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="6">
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11846</v>
+        <v>13051</v>
       </c>
       <c r="C6" t="n">
-        <v>4984</v>
+        <v>6056</v>
       </c>
       <c r="D6" t="n">
-        <v>2147</v>
+        <v>2679</v>
       </c>
       <c r="E6" t="n">
-        <v>43.08</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="7">
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7079</v>
+        <v>8137</v>
       </c>
       <c r="C7" t="n">
-        <v>5847</v>
+        <v>6933</v>
       </c>
       <c r="D7" t="n">
-        <v>370</v>
+        <v>451</v>
       </c>
       <c r="E7" t="n">
-        <v>6.33</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="8">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1745</v>
+        <v>1794</v>
       </c>
       <c r="C8" t="n">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="D8" t="n">
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>3.97</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="9">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1523</v>
+        <v>1603</v>
       </c>
       <c r="C9" t="n">
-        <v>548</v>
+        <v>635</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>5.84</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="10">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1234</v>
+        <v>1276</v>
       </c>
       <c r="C10" t="n">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>5.18</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="11">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1159</v>
+        <v>1195</v>
       </c>
       <c r="C11" t="n">
-        <v>462</v>
+        <v>504</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>4.55</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="12">
@@ -942,244 +942,244 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="C12" t="n">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Origen (7)</t>
+          <t>Origen (51)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>917</v>
+        <v>999</v>
       </c>
       <c r="C13" t="n">
-        <v>482</v>
+        <v>645</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>0.62</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Origen (625)</t>
+          <t>Origen (7)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>865</v>
+        <v>960</v>
       </c>
       <c r="C14" t="n">
-        <v>320</v>
+        <v>524</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3.12</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Origen (51)</t>
+          <t>Origen (625)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>786</v>
+        <v>904</v>
       </c>
       <c r="C15" t="n">
-        <v>437</v>
+        <v>363</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>1.37</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Origen (136)</t>
+          <t>Origen (702)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>698</v>
+        <v>889</v>
       </c>
       <c r="C16" t="n">
-        <v>260</v>
+        <v>419</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Origen (5)</t>
+          <t>Origen (73)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>697</v>
+        <v>744</v>
       </c>
       <c r="C17" t="n">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>4.48</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Origen (73)</t>
+          <t>Origen (136)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="C18" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>3.83</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Origen (443)</t>
+          <t>Origen (5)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>676</v>
+        <v>721</v>
       </c>
       <c r="C19" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>4.68</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Origen (882)</t>
+          <t>Origen (443)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>648</v>
+        <v>710</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Origen (702)</t>
+          <t>Origen (477)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="C21" t="n">
-        <v>171</v>
+        <v>409</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Origen (477)</t>
+          <t>Origen (882)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C22" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Origen (379)</t>
+          <t>Origen (297)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="C23" t="n">
-        <v>216</v>
+        <v>412</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>1.85</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Origen (297)</t>
+          <t>Origen (379)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="C24" t="n">
-        <v>364</v>
+        <v>242</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>0.55</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -1189,16 +1189,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="C25" t="n">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="26">
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="C26" t="n">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="27">
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="C27" t="n">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="28">
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="C28" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>5.15</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="29">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="C29" t="n">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="30">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C30" t="n">
         <v>12</v>
@@ -1303,16 +1303,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C31" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>6.59</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="32">
@@ -1322,16 +1322,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C32" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="33">
@@ -1341,54 +1341,54 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C33" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D33" t="n">
         <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>10.28</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Origen (40)</t>
+          <t>Origen (483)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C34" t="n">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>9.09</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Origen (483)</t>
+          <t>Origen (40)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C35" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>9.16</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="36">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C36" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.86</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="37">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C37" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -1455,16 +1455,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C39" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>14.04</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="40">
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C40" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>2.42</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="41">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C41" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C42" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.98</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="43">
@@ -1531,111 +1531,111 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Origen (115)</t>
+          <t>Origen (908)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C44" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>7.41</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Origen (502)</t>
+          <t>Origen (115)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>3.23</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Origen (890)</t>
+          <t>Origen (487)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Origen (285)</t>
+          <t>Origen (502)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C47" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Origen (908)</t>
+          <t>Origen (285)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="49">
@@ -1645,35 +1645,35 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Origen (397)</t>
+          <t>Origen (890)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/marketing_report/outputs/Grado_Pregrado/Informe_Analitico/Tablas_Informe_Analitico.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Informe_Analitico/Tablas_Informe_Analitico.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>398,401</t>
+          <t>398,289</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>305,011</t>
+          <t>305,126</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>169,894</t>
+          <t>170,007</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10,225</t>
+          <t>10,158</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7,980</t>
+          <t>7,937</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6,911</t>
+          <t>6,895</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7,993</t>
+          <t>7,984</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,377</t>
+          <t>1,388</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>153</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6,933</t>
+          <t>7,041</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>452</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238011</v>
+        <v>238084</v>
       </c>
       <c r="C2" t="n">
-        <v>128716</v>
+        <v>128786</v>
       </c>
       <c r="D2" t="n">
-        <v>3014</v>
+        <v>3002</v>
       </c>
       <c r="E2" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="3">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67000</v>
+        <v>67042</v>
       </c>
       <c r="C3" t="n">
-        <v>41178</v>
+        <v>41221</v>
       </c>
       <c r="D3" t="n">
-        <v>3897</v>
+        <v>3893</v>
       </c>
       <c r="E3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.44</v>
       </c>
     </row>
   </sheetData>
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201690</v>
+        <v>201693</v>
       </c>
       <c r="C2" t="n">
-        <v>117504</v>
+        <v>117506</v>
       </c>
       <c r="D2" t="n">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="E2" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="3">
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20625</v>
+        <v>20624</v>
       </c>
       <c r="C3" t="n">
-        <v>9186</v>
+        <v>9187</v>
       </c>
       <c r="D3" t="n">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E3" t="n">
-        <v>13.75</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="4">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19062</v>
+        <v>19063</v>
       </c>
       <c r="C4" t="n">
         <v>8197</v>
@@ -812,7 +812,7 @@
         <v>18679</v>
       </c>
       <c r="C5" t="n">
-        <v>11626</v>
+        <v>11627</v>
       </c>
       <c r="D5" t="n">
         <v>1258</v>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13051</v>
+        <v>13053</v>
       </c>
       <c r="C6" t="n">
-        <v>6056</v>
+        <v>6057</v>
       </c>
       <c r="D6" t="n">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="E6" t="n">
-        <v>44.24</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="7">
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8137</v>
+        <v>8247</v>
       </c>
       <c r="C7" t="n">
-        <v>6933</v>
+        <v>7041</v>
       </c>
       <c r="D7" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E7" t="n">
-        <v>6.51</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="8">
